--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104721_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104721_W30.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4825</v>
+        <v>5.8891</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0216</v>
+        <v>3.5309</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4609</v>
+        <v>2.3582</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8891</v>
+        <v>2.8849</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4563</v>
+        <v>3.4474</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5672</v>
+        <v>-0.5625</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5829</v>
+        <v>3.5684</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4338</v>
+        <v>3.4194</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1491</v>
+        <v>0.1489</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6938</v>
+        <v>-0.6835</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0225</v>
+        <v>0.028</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7163</v>
+        <v>-0.7114</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1163</v>
+        <v>1.5262</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6193</v>
+        <v>1.1494</v>
       </c>
       <c r="U2" t="n">
-        <v>0.497</v>
+        <v>0.3768</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7043</v>
+        <v>1.7057</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>0.613</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1911</v>
+        <v>5.4615</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5518</v>
+        <v>1.3022</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6393</v>
+        <v>4.1593</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7201</v>
+        <v>4.7144</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2068</v>
+        <v>4.2021</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5133</v>
+        <v>0.5123</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4332</v>
+        <v>3.4174</v>
       </c>
       <c r="K3" t="n">
-        <v>2.892</v>
+        <v>2.8818</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5412</v>
+        <v>0.5355</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2869</v>
+        <v>1.2971</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3148</v>
+        <v>1.3203</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0279</v>
+        <v>-0.0232</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7115</v>
+        <v>-0.4319</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1105</v>
+        <v>-0.3349</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.601</v>
+        <v>-0.097</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3919</v>
+        <v>3.7326</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1815</v>
+        <v>0.1742</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2104</v>
+        <v>3.5584</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8159</v>
+        <v>-0.8307</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3172</v>
+        <v>1.8607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5013</v>
+        <v>-2.6913</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4475</v>
+        <v>-0.3212</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4907</v>
+        <v>1.0719</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0433</v>
+        <v>-1.3931</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3684</v>
+        <v>-0.5095</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8264</v>
+        <v>0.7887</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.458</v>
+        <v>-1.2982</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1359</v>
+        <v>2.2763</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2719</v>
+        <v>3.4145</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8263</v>
+        <v>0.495</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2562</v>
+        <v>-0.1584</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6534</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3862</v>
+        <v>1.792</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3862</v>
+        <v>1.792</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>J. NUNEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0621</v>
+        <v>3.2085</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-1.1832</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7188</v>
+        <v>4.3917</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8368</v>
+        <v>6.8282</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8588</v>
+        <v>4.5697</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.6956</v>
+        <v>2.2585</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3139</v>
+        <v>4.8545</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0775</v>
+        <v>2.9335</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3914</v>
+        <v>1.921</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5228</v>
+        <v>1.9737</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7813</v>
+        <v>1.6361</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3042</v>
+        <v>0.3375</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2719</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>-5.9184</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4078</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1693</v>
+        <v>0.1119</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0032</v>
+        <v>-0.4348</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8338</v>
+        <v>0.5467</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7963</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7963</v>
+        <v>0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NUNEZ</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5461</v>
+        <v>2.4057</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8785</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4246</v>
+        <v>3.1703</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8317</v>
+        <v>0.8135</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5742</v>
+        <v>1.3105</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2575</v>
+        <v>-0.497</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8705</v>
+        <v>0.4335</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9438</v>
+        <v>0.4784</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9266</v>
+        <v>-0.0449</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9612</v>
+        <v>0.38</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6304</v>
+        <v>0.832</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3309</v>
+        <v>-0.4521</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.1806</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.9069</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7262</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5594</v>
+        <v>0.8411</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.161</v>
+        <v>0.3271</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6016</v>
+        <v>0.514</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5456</v>
+        <v>-0.387</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3188</v>
+        <v>-0.387</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8643999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9948</v>
+        <v>0.9668</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8319</v>
+        <v>0.5204</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8267</v>
+        <v>0.4464</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3854</v>
+        <v>2.4114</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1909</v>
+        <v>0.7896</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8055</v>
+        <v>1.6218</v>
       </c>
       <c r="J7" t="n">
-        <v>0.988</v>
+        <v>3.4136</v>
       </c>
       <c r="K7" t="n">
-        <v>1.665</v>
+        <v>1.7237</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6771</v>
+        <v>1.6899</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3974</v>
+        <v>-1.0022</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5259</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1285</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4544</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4991</v>
+        <v>-3.6421</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0447</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>1.768</v>
+        <v>0.287</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1328</v>
+        <v>0.2042</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6353</v>
+        <v>0.0827</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7043</v>
+        <v>0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4536</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4492</v>
+        <v>0.2188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2348</v>
+        <v>0.9298</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2143</v>
+        <v>-0.7109</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4146</v>
+        <v>-1.7859</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7889</v>
+        <v>-0.4454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6257</v>
+        <v>-1.3405</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4251</v>
+        <v>-0.1548</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7281</v>
+        <v>0.1584</v>
       </c>
       <c r="L8" t="n">
-        <v>1.697</v>
+        <v>-0.3132</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0104</v>
+        <v>-1.631</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9392</v>
+        <v>-0.6037</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0712</v>
+        <v>-1.0273</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.2719</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.635</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3631</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2392</v>
+        <v>0.5495</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1009</v>
+        <v>0.2228</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1383</v>
+        <v>0.3267</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5456</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3191</v>
+        <v>-0.1497</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5641</v>
+        <v>-2.187</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8831</v>
+        <v>2.0373</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7892</v>
+        <v>1.3861</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4471</v>
+        <v>2.1886</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3421</v>
+        <v>-0.8026</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1487</v>
+        <v>0.9801</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1616</v>
+        <v>1.658</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3102</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6405</v>
+        <v>0.406</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6086</v>
+        <v>0.5306</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0319</v>
+        <v>-0.1246</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9087</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2272</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1359</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0157</v>
+        <v>0.6251</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1513</v>
+        <v>-0.2047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1671</v>
+        <v>0.8299</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5456</v>
+        <v>-1.7057</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0913</v>
+        <v>-0.4584</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5456</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GONZALEZ</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9798</v>
+        <v>-0.6155</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8393</v>
+        <v>-0.3281</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1404</v>
+        <v>-0.2874</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0612</v>
+        <v>-1.3729</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1578</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.219</v>
+        <v>-0.7524</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7889</v>
+        <v>-0.6835</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.0689</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7889</v>
+        <v>-0.7524</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2723</v>
+        <v>-0.6895</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1578</v>
+        <v>-0.6895</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4301</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2272</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2272</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1458</v>
+        <v>0.4599</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0504</v>
+        <v>0.3553</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0953</v>
+        <v>0.1046</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>D. GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0371</v>
+        <v>-0.8155</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6825</v>
+        <v>-0.7711</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3546</v>
+        <v>-0.0444</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3737</v>
+        <v>-1.0606</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6221</v>
+        <v>0.1579</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7516</v>
+        <v>-1.2185</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6825</v>
+        <v>-0.7896</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06909999999999999</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7516</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6913</v>
+        <v>-0.271</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6913</v>
+        <v>0.1579</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.4289</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4544</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4544</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0416</v>
+        <v>0.0174</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.0185</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0416</v>
+        <v>-0.0011</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5054</v>
+        <v>-1.3743</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1864</v>
+        <v>-1.1196</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.319</v>
+        <v>-0.2546</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7456</v>
+        <v>-0.7447</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1372,31 +1372,31 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7456</v>
+        <v>-0.7447</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.1231</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0504</v>
+        <v>0.0185</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0416</v>
+        <v>0.1046</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1633</v>
+        <v>-1.7654</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4966</v>
+        <v>-3.2664</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3334</v>
+        <v>1.501</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.179</v>
+        <v>-2.1755</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8235</v>
+        <v>-1.8211</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3555</v>
+        <v>-0.3544</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1021</v>
+        <v>-2.1048</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3877</v>
+        <v>-1.3897</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.077</v>
+        <v>-0.0706</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4358</v>
+        <v>-0.4314</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3588</v>
+        <v>0.3608</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2115</v>
+        <v>0.1824</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0315</v>
+        <v>0.2042</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.18</v>
+        <v>-0.0218</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.113</v>
+        <v>17.1626</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.018199999999999</v>
+        <v>-3.162500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>20.1313</v>
+        <v>20.3253</v>
       </c>
       <c r="G14" t="n">
-        <v>11.2291</v>
+        <v>11.2261</v>
       </c>
       <c r="H14" t="n">
-        <v>15.81600000000001</v>
+        <v>15.7974</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.586900000000001</v>
+        <v>-4.5713</v>
       </c>
       <c r="J14" t="n">
-        <v>12.7111</v>
+        <v>12.6136</v>
       </c>
       <c r="K14" t="n">
-        <v>13.0739</v>
+        <v>13.0043</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3628999999999994</v>
+        <v>-0.3909999999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.482</v>
+        <v>-1.3873</v>
       </c>
       <c r="N14" t="n">
-        <v>2.742</v>
+        <v>2.7929</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.224</v>
+        <v>-4.1802</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.271900000000001</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.7187</v>
+        <v>-22.7632</v>
       </c>
       <c r="R14" t="n">
-        <v>20.4468</v>
+        <v>20.4869</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7224</v>
+        <v>4.786700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3490999999999999</v>
+        <v>1.3672</v>
       </c>
       <c r="U14" t="n">
-        <v>3.373499999999999</v>
+        <v>3.4195</v>
       </c>
       <c r="V14" t="n">
-        <v>3.4332</v>
+        <v>3.4261</v>
       </c>
       <c r="W14" t="n">
-        <v>5.6404</v>
+        <v>5.62</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2071</v>
+        <v>-2.1938</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6572</v>
+        <v>5.423</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4854</v>
+        <v>3.0401</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1718</v>
+        <v>2.3828</v>
       </c>
       <c r="G15" t="n">
-        <v>7.1545</v>
+        <v>7.1454</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0458</v>
+        <v>0.0485</v>
       </c>
       <c r="I15" t="n">
-        <v>7.1087</v>
+        <v>7.0969</v>
       </c>
       <c r="J15" t="n">
-        <v>7.5367</v>
+        <v>7.5171</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8874</v>
+        <v>0.8823</v>
       </c>
       <c r="L15" t="n">
-        <v>6.6494</v>
+        <v>6.6347</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3822</v>
+        <v>-0.3717</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8416</v>
+        <v>-0.8339</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4594</v>
+        <v>0.4622</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8622</v>
+        <v>-3.8697</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1845</v>
+        <v>-0.4054</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.508</v>
+        <v>-0.9227</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3235</v>
+        <v>0.5173</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0503</v>
+        <v>0.0488</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3188</v>
+        <v>0.3155</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2685</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.818</v>
+        <v>3.3908</v>
       </c>
       <c r="E16" t="n">
-        <v>1.23</v>
+        <v>1.2217</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5879</v>
+        <v>2.1691</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7614</v>
+        <v>0.765</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1593</v>
+        <v>-0.1556</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9207</v>
+        <v>0.9206</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2534</v>
+        <v>1.2501</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1037</v>
+        <v>0.1034</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1497</v>
+        <v>1.1467</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.492</v>
+        <v>-0.4851</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.263</v>
+        <v>-0.259</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.229</v>
+        <v>-0.226</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0384</v>
+        <v>0.5283</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0444</v>
+        <v>0.0414</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0828</v>
+        <v>0.4868</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0503</v>
+        <v>0.0488</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4887</v>
+        <v>0.7479</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7192</v>
+        <v>-2.3172</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2079</v>
+        <v>3.065</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0495</v>
+        <v>-2.048</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.7552</v>
+        <v>-2.7542</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7057</v>
+        <v>0.7062</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.2749</v>
+        <v>-2.2772</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.3494</v>
+        <v>-2.3517</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2254</v>
+        <v>0.2292</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4058</v>
+        <v>-0.4025</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6311</v>
+        <v>0.6317</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3349</v>
+        <v>0.5863</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5557</v>
+        <v>-0.04</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7792</v>
+        <v>0.6262</v>
       </c>
       <c r="V17" t="n">
-        <v>0.613</v>
+        <v>0.6162</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.613</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7317</v>
+        <v>-0.2583</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6016</v>
+        <v>0.398</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8699</v>
+        <v>-0.6563</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5371</v>
+        <v>1.5386</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5012</v>
+        <v>0.4999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0359</v>
+        <v>1.0387</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6838</v>
+        <v>3.6735</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3044</v>
+        <v>2.2958</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3794</v>
+        <v>1.3778</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1468</v>
+        <v>-2.135</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8033</v>
+        <v>-1.7959</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1947</v>
+        <v>0.2031</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5528</v>
+        <v>0.3665</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3581</v>
+        <v>-0.1634</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0481</v>
+        <v>-1.0123</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5302</v>
+        <v>-1.4297</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4822</v>
+        <v>0.4174</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1608</v>
+        <v>-2.159</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9159</v>
+        <v>-0.9136</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2449</v>
+        <v>-1.2455</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.448</v>
+        <v>-1.457</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0985</v>
+        <v>0.0927</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5465</v>
+        <v>-1.5497</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7128</v>
+        <v>-0.702</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0144</v>
+        <v>-1.0062</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3016</v>
+        <v>0.3043</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0416</v>
+        <v>0.0673</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7191</v>
+        <v>-0.6069</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7607</v>
+        <v>0.6741</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9736</v>
+        <v>-0.9692</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.0648</v>
+        <v>-2.0587</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.842</v>
+        <v>-2.2311</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.4577</v>
+        <v>-4.837</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6157</v>
+        <v>2.6059</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1388</v>
+        <v>-3.1412</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.7831</v>
+        <v>-5.7837</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6443</v>
+        <v>2.6425</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0982</v>
+        <v>-2.1102</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.8138</v>
+        <v>-4.8208</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7155</v>
+        <v>2.7106</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0405</v>
+        <v>-1.031</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.9629</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0712</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6829</v>
+        <v>0.2971</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3664</v>
+        <v>0.0063</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3165</v>
+        <v>0.2908</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2292</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7111</v>
+        <v>-2.7941</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9767</v>
+        <v>-2.5194</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.2746</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0388</v>
+        <v>-4.0368</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.278</v>
+        <v>-0.2734</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.7608</v>
+        <v>-3.7633</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5886</v>
+        <v>-1.5992</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7281</v>
+        <v>1.7237</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.3167</v>
+        <v>-3.3229</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4502</v>
+        <v>-2.4376</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0062</v>
+        <v>-1.9971</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.444</v>
+        <v>-0.4405</v>
       </c>
       <c r="P21" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6079</v>
+        <v>-0.697</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.161</v>
+        <v>-0.6926</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.447</v>
+        <v>-0.0044</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4473</v>
+        <v>-5.495</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9747</v>
+        <v>-4.2252</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4727</v>
+        <v>-1.2698</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5984</v>
+        <v>-3.5939</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5599</v>
+        <v>-2.5539</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0386</v>
+        <v>-1.04</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4506</v>
+        <v>-1.4561</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.426</v>
+        <v>-0.4277</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0246</v>
+        <v>-1.0284</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1479</v>
+        <v>-2.1378</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1339</v>
+        <v>-2.1262</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.014</v>
+        <v>-0.0116</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3767</v>
+        <v>-0.4264</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.025</v>
+        <v>-0.2652</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3516</v>
+        <v>-0.1612</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5425</v>
+        <v>-5.5808</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7208</v>
+        <v>-3.1576</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8217</v>
+        <v>-2.4231</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.9709</v>
       </c>
       <c r="H23" t="n">
         <v>-1.5192</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5483</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8245</v>
+        <v>1.8114</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6748</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>1.1497</v>
+        <v>1.1467</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7958</v>
+        <v>-2.7824</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.194</v>
+        <v>-2.1839</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6018</v>
+        <v>-0.5984</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.208</v>
+        <v>-1.2441</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.161</v>
+        <v>-0.5742</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0471</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2174</v>
+        <v>-5.9382</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.6145</v>
+        <v>-7.0434</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3971</v>
+        <v>1.1053</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.7244</v>
+        <v>-4.7252</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3923</v>
+        <v>-2.3922</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3321</v>
+        <v>-2.333</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.9561</v>
+        <v>-3.9651</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9496</v>
+        <v>-0.9555</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.0065</v>
+        <v>-3.0096</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7682</v>
+        <v>-0.7601</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4426</v>
+        <v>-1.4367</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6744</v>
+        <v>0.6766</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5612</v>
+        <v>-0.2812</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3187</v>
+        <v>-0.7321</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2424</v>
+        <v>0.4509</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.1128</v>
+        <v>-13.7481</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.6768</v>
+        <v>-20.8697</v>
       </c>
       <c r="F25" t="n">
-        <v>4.5639</v>
+        <v>7.121699999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-11.229</v>
+        <v>-11.226</v>
       </c>
       <c r="H25" t="n">
-        <v>-15.8159</v>
+        <v>-15.7974</v>
       </c>
       <c r="I25" t="n">
-        <v>4.586799999999998</v>
+        <v>4.5714</v>
       </c>
       <c r="J25" t="n">
-        <v>1.481999999999998</v>
+        <v>1.387300000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.7419</v>
+        <v>-2.793</v>
       </c>
       <c r="L25" t="n">
-        <v>4.224</v>
+        <v>4.180399999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-12.711</v>
+        <v>-12.6135</v>
       </c>
       <c r="N25" t="n">
-        <v>-13.0741</v>
+        <v>-13.0043</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3629999999999999</v>
+        <v>0.3911</v>
       </c>
       <c r="P25" t="n">
-        <v>2.272000000000001</v>
+        <v>2.276400000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-20.447</v>
+        <v>-20.4866</v>
       </c>
       <c r="R25" t="n">
-        <v>22.71879999999999</v>
+        <v>22.763</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.7226</v>
+        <v>-1.372</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.3735</v>
+        <v>-3.4195</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3490999999999999</v>
+        <v>2.0472</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.4332</v>
+        <v>-3.4261</v>
       </c>
       <c r="W25" t="n">
-        <v>1.6615</v>
+        <v>1.6492</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.0947</v>
+        <v>-5.0751</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104721_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104721_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-2.1938</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.0587</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104721_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-5.0751</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
